--- a/artfynd/A 55506-2022 artfynd.xlsx
+++ b/artfynd/A 55506-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55506-2022 artfynd.xlsx
+++ b/artfynd/A 55506-2022 artfynd.xlsx
@@ -675,56 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62196999</v>
+        <v>105556229</v>
       </c>
       <c r="B2" t="n">
-        <v>95246</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2604</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvigestad, V Gamleby, Sm</t>
+          <t>Brånestad, Odensvi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564503.0338944657</v>
+        <v>564477</v>
       </c>
       <c r="R2" t="n">
-        <v>6419597.806817609</v>
+        <v>6419658</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-11-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-11-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,82 +765,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Tholin</t>
+          <t>Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105556084</v>
+        <v>62196999</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Pfeiff.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brånestad, Odensvi, Sm</t>
+          <t>Kvigestad, V Gamleby, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564476.5124690325</v>
+        <v>564503</v>
       </c>
       <c r="R3" t="n">
-        <v>6419657.953655221</v>
+        <v>6419598</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-11-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,34 +866,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand</t>
+          <t>Michael Tholin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105556229</v>
+        <v>105556084</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564476.5124690325</v>
+        <v>564477</v>
       </c>
       <c r="R4" t="n">
-        <v>6419657.953655221</v>
+        <v>6419658</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +963,9 @@
           <t>2023-01-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
